--- a/data/trans_camb/P16A15-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A15-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 9,12</t>
+          <t>3,15; 9,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 8,71</t>
+          <t>2,88; 8,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,92</t>
+          <t>5,04; 11,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 8,76</t>
+          <t>2,24; 8,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 9,15</t>
+          <t>1,57; 8,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 10,15</t>
+          <t>4,51; 9,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 8,4</t>
+          <t>3,59; 8,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 7,74</t>
+          <t>3,3; 7,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,61; 9,9</t>
+          <t>5,74; 9,94</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,38; 192,95</t>
+          <t>40,89; 195,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,8; 187,96</t>
+          <t>37,4; 189,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,86; 230,2</t>
+          <t>65,97; 231,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,72; 124,03</t>
+          <t>21,94; 124,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,31; 137,45</t>
+          <t>14,66; 118,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,4; 155,47</t>
+          <t>43,17; 149,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,15; 133,2</t>
+          <t>45,02; 136,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,13; 125,14</t>
+          <t>40,94; 129,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68,14; 159,21</t>
+          <t>69,91; 167,64</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,77</t>
+          <t>1,85; 6,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,23</t>
+          <t>1,29; 6,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 6,56</t>
+          <t>-1,77; 6,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 5,38</t>
+          <t>-0,27; 5,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 5,69</t>
+          <t>0,12; 5,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,01</t>
+          <t>2,02; 7,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,36</t>
+          <t>1,24; 5,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,26</t>
+          <t>1,43; 5,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 5,7</t>
+          <t>-0,54; 5,73</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,56; 139,38</t>
+          <t>25,6; 144,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,25; 129,41</t>
+          <t>17,44; 132,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,87; 128,55</t>
+          <t>-27,47; 117,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 69,37</t>
+          <t>-1,54; 69,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 78,13</t>
+          <t>2,7; 81,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,29; 90,82</t>
+          <t>17,88; 91,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,65; 80,56</t>
+          <t>14,92; 76,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,63; 81,02</t>
+          <t>16,75; 74,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 80,06</t>
+          <t>0,57; 84,12</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 6,73</t>
+          <t>0,89; 6,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 6,77</t>
+          <t>1,19; 6,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,87; 9,72</t>
+          <t>3,85; 10,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 8,53</t>
+          <t>1,96; 8,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 3,2</t>
+          <t>-2,71; 3,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 56,1</t>
+          <t>2,99; 61,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,66</t>
+          <t>2,55; 6,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,37</t>
+          <t>0,3; 4,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 42,96</t>
+          <t>4,73; 47,28</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,41; 161,79</t>
+          <t>9,6; 152,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,72; 153,77</t>
+          <t>15,38; 165,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50,8; 223,56</t>
+          <t>51,49; 229,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27,44; 144,75</t>
+          <t>17,72; 132,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,3; 51,89</t>
+          <t>-31,0; 52,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,82; 895,88</t>
+          <t>36,28; 1022,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,98; 118,13</t>
+          <t>32,71; 117,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 78,64</t>
+          <t>3,78; 77,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65,85; 690,89</t>
+          <t>68,94; 750,75</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,85</t>
+          <t>1,53; 6,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,71</t>
+          <t>-0,71; 3,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,23; 8,89</t>
+          <t>4,14; 8,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,13</t>
+          <t>2,26; 7,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,45</t>
+          <t>1,19; 6,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,2; 9,92</t>
+          <t>4,14; 9,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,46</t>
+          <t>2,8; 6,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,49</t>
+          <t>0,98; 4,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,78</t>
+          <t>4,64; 8,59</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,7; 137,44</t>
+          <t>20,66; 135,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 73,56</t>
+          <t>-11,0; 77,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58,05; 177,98</t>
+          <t>58,28; 180,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27,06; 126,59</t>
+          <t>26,49; 133,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,5; 111,93</t>
+          <t>15,56; 110,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,04; 175,49</t>
+          <t>53,04; 170,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,13; 115,71</t>
+          <t>39,7; 111,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,41; 80,2</t>
+          <t>13,19; 78,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>74,73; 158,18</t>
+          <t>69,36; 153,64</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,76</t>
+          <t>3,22; 5,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,85</t>
+          <t>2,31; 4,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,37; 7,25</t>
+          <t>2,3; 7,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,75</t>
+          <t>2,93; 5,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,57</t>
+          <t>1,68; 4,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,5; 26,72</t>
+          <t>5,36; 23,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,45; 5,45</t>
+          <t>3,34; 5,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,39</t>
+          <t>2,41; 4,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,37; 17,71</t>
+          <t>5,29; 17,69</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>47,88; 110,72</t>
+          <t>50,08; 111,49</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>36,33; 92,83</t>
+          <t>35,68; 95,1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56,76; 137,98</t>
+          <t>41,41; 133,74</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32,37; 78,8</t>
+          <t>34,92; 82,3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>19,12; 62,36</t>
+          <t>19,17; 62,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,62; 347,52</t>
+          <t>65,32; 308,96</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,58; 83,89</t>
+          <t>46,5; 84,27</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>31,85; 67,24</t>
+          <t>33,25; 68,66</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>76,44; 274,75</t>
+          <t>76,77; 271,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A15-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A15-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,93</t>
+          <t>7,64</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>6,89</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,62</t>
+          <t>7,3</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,15; 9,39</t>
+          <t>3,16; 9,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 8,89</t>
+          <t>2,91; 8,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 11,09</t>
+          <t>4,71; 10,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,81</t>
+          <t>2,2; 9,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,46</t>
+          <t>1,85; 8,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 9,85</t>
+          <t>4,18; 9,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,59; 8,22</t>
+          <t>3,38; 7,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 7,7</t>
+          <t>3,39; 7,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,74; 9,94</t>
+          <t>5,28; 9,38</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>134,74%</t>
+          <t>129,87%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>107,07%</t>
+          <t>102,52%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,89; 195,19</t>
+          <t>40,1; 200,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,4; 189,52</t>
+          <t>38,33; 187,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,97; 231,17</t>
+          <t>62,21; 226,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,94; 124,46</t>
+          <t>21,36; 129,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,66; 118,87</t>
+          <t>18,63; 137,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,17; 149,66</t>
+          <t>42,14; 144,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,02; 136,01</t>
+          <t>40,65; 130,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,94; 129,68</t>
+          <t>41,46; 127,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>69,91; 167,64</t>
+          <t>63,06; 158,1</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,18</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>4,31</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>4,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,74</t>
+          <t>1,74; 6,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,22</t>
+          <t>1,42; 6,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 6,26</t>
+          <t>2,93; 7,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 5,28</t>
+          <t>-0,44; 5,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,94</t>
+          <t>0,01; 5,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 7,02</t>
+          <t>1,54; 6,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,16</t>
+          <t>1,44; 5,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,09</t>
+          <t>1,43; 5,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,73</t>
+          <t>3,03; 6,44</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>64,17%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,6; 144,42</t>
+          <t>22,16; 131,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,44; 132,34</t>
+          <t>19,13; 129,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,47; 117,85</t>
+          <t>38,55; 159,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 69,82</t>
+          <t>-5,07; 66,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 81,2</t>
+          <t>0,03; 74,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,88; 91,71</t>
+          <t>14,16; 83,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,92; 76,46</t>
+          <t>16,86; 77,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,75; 74,12</t>
+          <t>16,92; 80,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 84,12</t>
+          <t>36,27; 101,18</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,71</t>
+          <t>6,44</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,38</t>
+          <t>4,06</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16,34</t>
+          <t>5,24</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 6,49</t>
+          <t>0,87; 6,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,79</t>
+          <t>1,27; 6,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 10,17</t>
+          <t>3,66; 9,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 8,19</t>
+          <t>2,04; 8,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 3,26</t>
+          <t>-2,32; 3,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 61,35</t>
+          <t>1,27; 6,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,61</t>
+          <t>2,51; 6,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,18</t>
+          <t>0,26; 4,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,73; 47,28</t>
+          <t>3,42; 7,46</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>122,04%</t>
+          <t>117,17%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>315,79%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>253,19%</t>
+          <t>81,23%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,6; 152,41</t>
+          <t>11,6; 155,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,38; 165,42</t>
+          <t>19,41; 166,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51,49; 229,98</t>
+          <t>51,01; 228,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,72; 132,14</t>
+          <t>22,68; 139,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,0; 52,05</t>
+          <t>-27,04; 53,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,28; 1022,69</t>
+          <t>12,95; 114,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,71; 117,19</t>
+          <t>31,35; 125,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,78; 77,41</t>
+          <t>3,94; 77,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>68,94; 750,75</t>
+          <t>44,29; 141,27</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,39</t>
+          <t>5,91</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,42</t>
+          <t>8,42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,96</t>
+          <t>7,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,8</t>
+          <t>1,99; 6,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 3,94</t>
+          <t>-0,63; 3,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,14; 8,9</t>
+          <t>3,47; 8,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,47</t>
+          <t>2,32; 7,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,5</t>
+          <t>1,33; 6,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,14; 9,76</t>
+          <t>6,0; 10,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,38</t>
+          <t>2,67; 6,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,48</t>
+          <t>1,09; 4,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,64; 8,59</t>
+          <t>5,61; 8,87</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106,87%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>109,14%</t>
+          <t>123,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>108,61%</t>
+          <t>113,14%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,66; 135,28</t>
+          <t>28,19; 140,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 77,48</t>
+          <t>-9,42; 73,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58,28; 180,42</t>
+          <t>51,03; 172,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26,49; 133,69</t>
+          <t>26,61; 131,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,56; 110,67</t>
+          <t>16,27; 112,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,04; 170,16</t>
+          <t>73,5; 190,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,7; 111,91</t>
+          <t>37,59; 117,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,19; 78,35</t>
+          <t>14,98; 80,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>69,36; 153,64</t>
+          <t>76,43; 156,4</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>6,17</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,65</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,22</t>
+          <t>6,09</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,82</t>
+          <t>3,18; 5,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,95</t>
+          <t>2,29; 4,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,16</t>
+          <t>4,9; 7,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,9</t>
+          <t>2,86; 5,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,5</t>
+          <t>1,64; 4,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,36; 23,95</t>
+          <t>4,74; 7,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,37</t>
+          <t>3,52; 5,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,38</t>
+          <t>2,32; 4,32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,29; 17,69</t>
+          <t>5,07; 7,02</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>106,02%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>134,93%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>119,62%</t>
+          <t>88,62%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>50,08; 111,49</t>
+          <t>49,76; 112,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>35,68; 95,1</t>
+          <t>35,47; 90,41</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>41,41; 133,74</t>
+          <t>76,19; 143,26</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34,92; 82,3</t>
+          <t>32,68; 80,25</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>19,17; 62,35</t>
+          <t>18,33; 62,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,32; 308,96</t>
+          <t>55,16; 104,48</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,5; 84,27</t>
+          <t>47,78; 84,04</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>33,25; 68,66</t>
+          <t>31,61; 66,92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>76,77; 271,6</t>
+          <t>68,32; 109,89</t>
         </is>
       </c>
     </row>
